--- a/test/list/sukamantri/mekarwangi/list_mekarwangi_1.xlsx
+++ b/test/list/sukamantri/mekarwangi/list_mekarwangi_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\sukamantri\mekarwangi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5D25B-2697-4824-A492-14D91614FC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1384C5A6-430B-4E08-AEEE-319DE4ABB13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="139">
   <si>
     <t>nama</t>
   </si>
@@ -184,88 +184,265 @@
     <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
   </si>
   <si>
-    <t>2023-09-01</t>
-  </si>
-  <si>
-    <t>2023-09-02</t>
-  </si>
-  <si>
-    <t>2023-09-04</t>
-  </si>
-  <si>
-    <t>2023-09-05</t>
-  </si>
-  <si>
-    <t>EMAY MARYATI</t>
-  </si>
-  <si>
-    <t>MIA NURUL KHORIYAH</t>
-  </si>
-  <si>
-    <t>IPAN NURDIN</t>
-  </si>
-  <si>
-    <t>RASJA SUPRIATNA</t>
-  </si>
-  <si>
-    <t>MUMUN MUNAWAROH</t>
-  </si>
-  <si>
-    <t>MUHAMMAD FARHANULIBAD</t>
-  </si>
-  <si>
-    <t>AZKIA TRI AMALIA</t>
-  </si>
-  <si>
-    <t>AHIDIN</t>
-  </si>
-  <si>
-    <t>ETI</t>
-  </si>
-  <si>
-    <t>ADE RIZAL</t>
-  </si>
-  <si>
-    <t>TATA</t>
-  </si>
-  <si>
-    <t>CARSIH</t>
-  </si>
-  <si>
-    <t>SOLIHIN</t>
-  </si>
-  <si>
-    <t>ENTIN</t>
-  </si>
-  <si>
-    <t>SARJONO</t>
-  </si>
-  <si>
-    <t>YUMYATI</t>
-  </si>
-  <si>
-    <t>YESCAL MAULANA</t>
-  </si>
-  <si>
-    <t>JAKA</t>
-  </si>
-  <si>
-    <t>EROH</t>
-  </si>
-  <si>
-    <t>IBAD BADRIYA</t>
-  </si>
-  <si>
-    <t>YEYEN YUNINGSIH</t>
-  </si>
-  <si>
-    <t>DAHYA</t>
-  </si>
-  <si>
-    <t>WIWIN</t>
-  </si>
-  <si>
-    <t>ENJANG AQIL</t>
+    <t>2023-10-01</t>
+  </si>
+  <si>
+    <t>2023-10-02</t>
+  </si>
+  <si>
+    <t>2023-10-03</t>
+  </si>
+  <si>
+    <t>2023-10-04</t>
+  </si>
+  <si>
+    <t>2023-10-05</t>
+  </si>
+  <si>
+    <t>2023-10-06</t>
+  </si>
+  <si>
+    <t>2023-10-07</t>
+  </si>
+  <si>
+    <t>2023-10-09</t>
+  </si>
+  <si>
+    <t>YAYAH SITI ROKAYAH</t>
+  </si>
+  <si>
+    <t>KARTIWA</t>
+  </si>
+  <si>
+    <t>SAONAH</t>
+  </si>
+  <si>
+    <t>MAKSUM</t>
+  </si>
+  <si>
+    <t>ROPIAH</t>
+  </si>
+  <si>
+    <t>AHMAD PAUJI</t>
+  </si>
+  <si>
+    <t>ABDUL WAHAB</t>
+  </si>
+  <si>
+    <t>NURAENI</t>
+  </si>
+  <si>
+    <t>SITI UMAYAH</t>
+  </si>
+  <si>
+    <t>SRI WAHYUNI</t>
+  </si>
+  <si>
+    <t>SAMSUL BAHRI</t>
+  </si>
+  <si>
+    <t>HANI</t>
+  </si>
+  <si>
+    <t>ATEP DANDI</t>
+  </si>
+  <si>
+    <t>MUHAMAD FAISAL AJIZ</t>
+  </si>
+  <si>
+    <t>DANI</t>
+  </si>
+  <si>
+    <t>ABDUL GANI</t>
+  </si>
+  <si>
+    <t>CANTIMAH</t>
+  </si>
+  <si>
+    <t>AHMAD MAULANA</t>
+  </si>
+  <si>
+    <t>MUSLIH</t>
+  </si>
+  <si>
+    <t>MIMIN KARTIMI</t>
+  </si>
+  <si>
+    <t>JIAN NASRULAH</t>
+  </si>
+  <si>
+    <t>MULYANA</t>
+  </si>
+  <si>
+    <t>KUSEN</t>
+  </si>
+  <si>
+    <t>NANA SURYANA</t>
+  </si>
+  <si>
+    <t>EHAT SUTIHAT</t>
+  </si>
+  <si>
+    <t>USUP</t>
+  </si>
+  <si>
+    <t>TITIN ROHAYATIN</t>
+  </si>
+  <si>
+    <t>TARSA</t>
+  </si>
+  <si>
+    <t>KARTINI</t>
+  </si>
+  <si>
+    <t>EBO</t>
+  </si>
+  <si>
+    <t>DARSIH</t>
+  </si>
+  <si>
+    <t>MAMAN DARMANSYAH</t>
+  </si>
+  <si>
+    <t>ILYAS SY</t>
+  </si>
+  <si>
+    <t>LINA HERLINA</t>
+  </si>
+  <si>
+    <t>DANI HIDAYAT</t>
+  </si>
+  <si>
+    <t>TAHYUDIN</t>
+  </si>
+  <si>
+    <t>HERNAWATI</t>
+  </si>
+  <si>
+    <t>SIPA SITI SAADAH</t>
+  </si>
+  <si>
+    <t>ALIYA TRI DZAKIYYAH</t>
+  </si>
+  <si>
+    <t>TOLIB</t>
+  </si>
+  <si>
+    <t>MIMIN</t>
+  </si>
+  <si>
+    <t>SUANDA</t>
+  </si>
+  <si>
+    <t>KUSNI'AH</t>
+  </si>
+  <si>
+    <t>IKMAL MAULANA</t>
+  </si>
+  <si>
+    <t>DAUD</t>
+  </si>
+  <si>
+    <t>IDAH WASIDAH</t>
+  </si>
+  <si>
+    <t>WINDI HERDIANTI</t>
+  </si>
+  <si>
+    <t>AGUS SATRIADI</t>
+  </si>
+  <si>
+    <t>ANI SUSILAWATI</t>
+  </si>
+  <si>
+    <t>ADI NURSATRIADI</t>
+  </si>
+  <si>
+    <t>LIKA ARDANA PUTRI</t>
+  </si>
+  <si>
+    <t>ARIFIN</t>
+  </si>
+  <si>
+    <t>IBNU UBAEDILAH</t>
+  </si>
+  <si>
+    <t>YUSUP MAHARDIKA</t>
+  </si>
+  <si>
+    <t>SAEPUDIN</t>
+  </si>
+  <si>
+    <t>kendaraan umum yang sulit dijumpai di wilayah terpencil.</t>
+  </si>
+  <si>
+    <t>Kualitas jaringan telepon seluler buruk di beberapa area.</t>
+  </si>
+  <si>
+    <t>Minimnya jalur sepeda membuat sulit bagi pengendara sepeda.</t>
+  </si>
+  <si>
+    <t>kondisi jalan yang kumuh dan tidak terawat rawan-.</t>
+  </si>
+  <si>
+    <t>Kelistrikan sering terganggu akibat cuaca ekstrem.</t>
+  </si>
+  <si>
+    <t>Pembangunan trotoar yang tidak merata dan berbahaya.</t>
+  </si>
+  <si>
+    <t>Tidak ada jalur khusus transportasi umum, menyebabkan kemacetan.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat penampungan untuk hewan jalanan di jalan.</t>
+  </si>
+  <si>
+    <t>Pipa air tua sering bocor dan mengganggu pasokan air.</t>
+  </si>
+  <si>
+    <t>Keterbatasan aksesibilitas bagi penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Minimnya tempat parkir untuk kendaraan umum di tempat kami.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan pendapatan dan kesenjangan sosial yang semakin lebar, menciptakan keresahan di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap layanan kesehatan berkualitas, membuat banyak orang kesulitan mendapatkan perawatan yang dibutuhkan.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja dan peluang ekonomi yang memadai, meningkatkan tingkat pengangguran dan ketidakpastian pekerjaan.</t>
+  </si>
+  <si>
+    <t>Sistem pendidikan yang tidak merata dan kurang berkualitas, menghambat kemajuan sosial dan ekonomi bagi sebagian masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Jalan tidak ramah lingkungan, tanpa pohon atau taman penyerap polusi.</t>
+  </si>
+  <si>
+    <t>Marka jalan yang pudar atau tidak terlihat jelas, meningkatkan risiko kecelakaan.</t>
+  </si>
+  <si>
+    <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
   </si>
 </sst>
 </file>
@@ -275,7 +452,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,14 +473,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -332,7 +501,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -340,7 +509,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -656,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -700,7 +868,7 @@
         <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -708,11 +876,11 @@
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>002</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>014</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>conf!$A$2</f>
@@ -730,19 +898,19 @@
         <v>52</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>003</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>009</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>conf!$A$2</f>
@@ -760,19 +928,19 @@
         <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>003</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>008</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>conf!$A$2</f>
@@ -790,7 +958,7 @@
         <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -798,11 +966,11 @@
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>015</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>005</v>
       </c>
       <c r="G5" s="4" t="str">
         <f>conf!$A$2</f>
@@ -820,19 +988,19 @@
         <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>015</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>conf!$A$2</f>
@@ -850,19 +1018,19 @@
         <v>52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>008</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>001</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>conf!$A$2</f>
@@ -877,10 +1045,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -888,11 +1056,11 @@
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>009</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="G8" s="4" t="str">
         <f>conf!$A$2</f>
@@ -910,19 +1078,19 @@
         <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>003</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>conf!$A$2</f>
@@ -940,19 +1108,19 @@
         <v>53</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>008</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="G10" s="4" t="str">
         <f>conf!$A$2</f>
@@ -970,11 +1138,11 @@
         <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -982,7 +1150,7 @@
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1000,19 +1168,19 @@
         <v>53</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>001</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>002</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1030,19 +1198,19 @@
         <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>007</v>
-      </c>
-      <c r="F13" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1057,18 +1225,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1087,22 +1255,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>003</v>
-      </c>
-      <c r="F15" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1120,15 +1288,15 @@
         <v>54</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1150,15 +1318,15 @@
         <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>005</v>
       </c>
       <c r="F17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1180,7 +1348,7 @@
         <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1188,11 +1356,11 @@
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>015</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>015</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1210,7 +1378,7 @@
         <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1218,11 +1386,11 @@
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>007</v>
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>009</v>
       </c>
       <c r="G19" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1237,22 +1405,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>004</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>004</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1267,22 +1435,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>010</v>
       </c>
       <c r="F21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>010</v>
       </c>
       <c r="G21" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1297,14 +1465,14 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1312,7 +1480,7 @@
       </c>
       <c r="F22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>009</v>
       </c>
       <c r="G22" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1330,19 +1498,19 @@
         <v>55</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>013</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>008</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1360,19 +1528,19 @@
         <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>013</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>002</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1390,7 +1558,7 @@
         <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1402,7 +1570,7 @@
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>007</v>
       </c>
       <c r="G25" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1412,10 +1580,869 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B41" s="5"/>
-      <c r="D41" s="1"/>
-      <c r="F41"/>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G27" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G29" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G30" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G31" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G32" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G33" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G34" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G35" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G36" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H36" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G37" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H37" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G38" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G39" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G40" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H40" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G41" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G42" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G43" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G44" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G45" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H45" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G46" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G47" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G48" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G49" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G50" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H50" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G51" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G52" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H52" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G53" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H53" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G54" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H54" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G55" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H55" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G56" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H56" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G57" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H57" t="s">
+        <v>138</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test/list/sukamantri/mekarwangi/list_mekarwangi_1.xlsx
+++ b/test/list/sukamantri/mekarwangi/list_mekarwangi_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\sukamantri\mekarwangi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1384C5A6-430B-4E08-AEEE-319DE4ABB13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C284687-AB32-43A4-95EA-80C85BDEC775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="conf" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="197">
   <si>
     <t>nama</t>
   </si>
@@ -184,195 +195,6 @@
     <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
   </si>
   <si>
-    <t>2023-10-01</t>
-  </si>
-  <si>
-    <t>2023-10-02</t>
-  </si>
-  <si>
-    <t>2023-10-03</t>
-  </si>
-  <si>
-    <t>2023-10-04</t>
-  </si>
-  <si>
-    <t>2023-10-05</t>
-  </si>
-  <si>
-    <t>2023-10-06</t>
-  </si>
-  <si>
-    <t>2023-10-07</t>
-  </si>
-  <si>
-    <t>2023-10-09</t>
-  </si>
-  <si>
-    <t>YAYAH SITI ROKAYAH</t>
-  </si>
-  <si>
-    <t>KARTIWA</t>
-  </si>
-  <si>
-    <t>SAONAH</t>
-  </si>
-  <si>
-    <t>MAKSUM</t>
-  </si>
-  <si>
-    <t>ROPIAH</t>
-  </si>
-  <si>
-    <t>AHMAD PAUJI</t>
-  </si>
-  <si>
-    <t>ABDUL WAHAB</t>
-  </si>
-  <si>
-    <t>NURAENI</t>
-  </si>
-  <si>
-    <t>SITI UMAYAH</t>
-  </si>
-  <si>
-    <t>SRI WAHYUNI</t>
-  </si>
-  <si>
-    <t>SAMSUL BAHRI</t>
-  </si>
-  <si>
-    <t>HANI</t>
-  </si>
-  <si>
-    <t>ATEP DANDI</t>
-  </si>
-  <si>
-    <t>MUHAMAD FAISAL AJIZ</t>
-  </si>
-  <si>
-    <t>DANI</t>
-  </si>
-  <si>
-    <t>ABDUL GANI</t>
-  </si>
-  <si>
-    <t>CANTIMAH</t>
-  </si>
-  <si>
-    <t>AHMAD MAULANA</t>
-  </si>
-  <si>
-    <t>MUSLIH</t>
-  </si>
-  <si>
-    <t>MIMIN KARTIMI</t>
-  </si>
-  <si>
-    <t>JIAN NASRULAH</t>
-  </si>
-  <si>
-    <t>MULYANA</t>
-  </si>
-  <si>
-    <t>KUSEN</t>
-  </si>
-  <si>
-    <t>NANA SURYANA</t>
-  </si>
-  <si>
-    <t>EHAT SUTIHAT</t>
-  </si>
-  <si>
-    <t>USUP</t>
-  </si>
-  <si>
-    <t>TITIN ROHAYATIN</t>
-  </si>
-  <si>
-    <t>TARSA</t>
-  </si>
-  <si>
-    <t>KARTINI</t>
-  </si>
-  <si>
-    <t>EBO</t>
-  </si>
-  <si>
-    <t>DARSIH</t>
-  </si>
-  <si>
-    <t>MAMAN DARMANSYAH</t>
-  </si>
-  <si>
-    <t>ILYAS SY</t>
-  </si>
-  <si>
-    <t>LINA HERLINA</t>
-  </si>
-  <si>
-    <t>DANI HIDAYAT</t>
-  </si>
-  <si>
-    <t>TAHYUDIN</t>
-  </si>
-  <si>
-    <t>HERNAWATI</t>
-  </si>
-  <si>
-    <t>SIPA SITI SAADAH</t>
-  </si>
-  <si>
-    <t>ALIYA TRI DZAKIYYAH</t>
-  </si>
-  <si>
-    <t>TOLIB</t>
-  </si>
-  <si>
-    <t>MIMIN</t>
-  </si>
-  <si>
-    <t>SUANDA</t>
-  </si>
-  <si>
-    <t>KUSNI'AH</t>
-  </si>
-  <si>
-    <t>IKMAL MAULANA</t>
-  </si>
-  <si>
-    <t>DAUD</t>
-  </si>
-  <si>
-    <t>IDAH WASIDAH</t>
-  </si>
-  <si>
-    <t>WINDI HERDIANTI</t>
-  </si>
-  <si>
-    <t>AGUS SATRIADI</t>
-  </si>
-  <si>
-    <t>ANI SUSILAWATI</t>
-  </si>
-  <si>
-    <t>ADI NURSATRIADI</t>
-  </si>
-  <si>
-    <t>LIKA ARDANA PUTRI</t>
-  </si>
-  <si>
-    <t>ARIFIN</t>
-  </si>
-  <si>
-    <t>IBNU UBAEDILAH</t>
-  </si>
-  <si>
-    <t>YUSUP MAHARDIKA</t>
-  </si>
-  <si>
-    <t>SAEPUDIN</t>
-  </si>
-  <si>
     <t>kendaraan umum yang sulit dijumpai di wilayah terpencil.</t>
   </si>
   <si>
@@ -443,6 +265,369 @@
   </si>
   <si>
     <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
+  </si>
+  <si>
+    <t>2023-11-01</t>
+  </si>
+  <si>
+    <t>2023-11-02</t>
+  </si>
+  <si>
+    <t>2023-11-03</t>
+  </si>
+  <si>
+    <t>2023-11-04</t>
+  </si>
+  <si>
+    <t>2023-11-06</t>
+  </si>
+  <si>
+    <t>2023-11-07</t>
+  </si>
+  <si>
+    <t>2023-11-08</t>
+  </si>
+  <si>
+    <t>2023-11-09</t>
+  </si>
+  <si>
+    <t>2023-11-10</t>
+  </si>
+  <si>
+    <t>ANISA PUTRI MARWAH</t>
+  </si>
+  <si>
+    <t>MAESAROH</t>
+  </si>
+  <si>
+    <t>ELIS SURYANI</t>
+  </si>
+  <si>
+    <t>AEP ABDUL RAHMAN</t>
+  </si>
+  <si>
+    <t>YANTI YULIAWATI</t>
+  </si>
+  <si>
+    <t>NAUFAL ADITYA RAMADHAN</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RAIHAN AHZA</t>
+  </si>
+  <si>
+    <t>BUDIMAN</t>
+  </si>
+  <si>
+    <t>ERAT RATNASARI</t>
+  </si>
+  <si>
+    <t>INTAN NURAINI</t>
+  </si>
+  <si>
+    <t>EROH</t>
+  </si>
+  <si>
+    <t>IMAT ISMATULLOH</t>
+  </si>
+  <si>
+    <t>ENDED DEDI</t>
+  </si>
+  <si>
+    <t>ENUNG NURALIAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD RAIHAN MUZAKKI</t>
+  </si>
+  <si>
+    <t>MUHAMAD ZAHFAL NURFUADI</t>
+  </si>
+  <si>
+    <t>RISMAYANTIKA</t>
+  </si>
+  <si>
+    <t>REZKY KEYLA RIVANA</t>
+  </si>
+  <si>
+    <t>DEDI AHMAD MAWARDI</t>
+  </si>
+  <si>
+    <t>IRMAYANTI</t>
+  </si>
+  <si>
+    <t>ALFAN FARIS FADILAH</t>
+  </si>
+  <si>
+    <t>IRPAN</t>
+  </si>
+  <si>
+    <t>RATNASARI</t>
+  </si>
+  <si>
+    <t>IRSYAD MEKKA ELVANO</t>
+  </si>
+  <si>
+    <t>HASIM</t>
+  </si>
+  <si>
+    <t>SOPIAH</t>
+  </si>
+  <si>
+    <t>AZKYA SEPTIA ANGGRAENI</t>
+  </si>
+  <si>
+    <t>NURUL HIDAYAH</t>
+  </si>
+  <si>
+    <t>ABDUL</t>
+  </si>
+  <si>
+    <t>WAKIAH</t>
+  </si>
+  <si>
+    <t>ISNAN MUHAMAD ABDULLAH</t>
+  </si>
+  <si>
+    <t>DEDE NURUL AZMI</t>
+  </si>
+  <si>
+    <t>WATMA</t>
+  </si>
+  <si>
+    <t>WASIH</t>
+  </si>
+  <si>
+    <t>HARYADI</t>
+  </si>
+  <si>
+    <t>ENTIN</t>
+  </si>
+  <si>
+    <t>DADAN PRAYOGA</t>
+  </si>
+  <si>
+    <t>SAMSU</t>
+  </si>
+  <si>
+    <t>WATINI</t>
+  </si>
+  <si>
+    <t>ANDI HERMAWAN</t>
+  </si>
+  <si>
+    <t>DAYAT HIDAYAT</t>
+  </si>
+  <si>
+    <t>EMAH</t>
+  </si>
+  <si>
+    <t>AYUB</t>
+  </si>
+  <si>
+    <t>SITI MARYAM</t>
+  </si>
+  <si>
+    <t>DEDE SITI SILVIA</t>
+  </si>
+  <si>
+    <t>NURHOLIPAH</t>
+  </si>
+  <si>
+    <t>EMUS</t>
+  </si>
+  <si>
+    <t>ADE KUSMAWATI</t>
+  </si>
+  <si>
+    <t>RIYEN NURAENI</t>
+  </si>
+  <si>
+    <t>DIKA HADI RAHMANDA</t>
+  </si>
+  <si>
+    <t>OHAN</t>
+  </si>
+  <si>
+    <t>ADE NURLAELA</t>
+  </si>
+  <si>
+    <t>HILMI UBAIDILLAH</t>
+  </si>
+  <si>
+    <t>HILMAN ABDILLAH</t>
+  </si>
+  <si>
+    <t>ABDUL GOPAR</t>
+  </si>
+  <si>
+    <t>YANTI</t>
+  </si>
+  <si>
+    <t>FARIDATUL MUSYAROPAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD ALBAR</t>
+  </si>
+  <si>
+    <t>SYARIP</t>
+  </si>
+  <si>
+    <t>MARIAMAH</t>
+  </si>
+  <si>
+    <t>AJIS SUTISNA</t>
+  </si>
+  <si>
+    <t>HIDIR</t>
+  </si>
+  <si>
+    <t>ERAH</t>
+  </si>
+  <si>
+    <t>HERAWATI</t>
+  </si>
+  <si>
+    <t>ODIH SAPUTRA</t>
+  </si>
+  <si>
+    <t>NUNUNG NURJANAH</t>
+  </si>
+  <si>
+    <t>RAPLI AKBAR PADILAH</t>
+  </si>
+  <si>
+    <t>WAHIDIN</t>
+  </si>
+  <si>
+    <t>ATISAH</t>
+  </si>
+  <si>
+    <t>SITI RAHMAWATI</t>
+  </si>
+  <si>
+    <t>NURHIDAYAT</t>
+  </si>
+  <si>
+    <t>DAHIRIN</t>
+  </si>
+  <si>
+    <t>KARSIH</t>
+  </si>
+  <si>
+    <t>MUHAMAD  TAUFIK HIDAYAT</t>
+  </si>
+  <si>
+    <t>AGUNG</t>
+  </si>
+  <si>
+    <t>UJED</t>
+  </si>
+  <si>
+    <t>ROKAYAH</t>
+  </si>
+  <si>
+    <t>HAMIM</t>
+  </si>
+  <si>
+    <t>MAE MUNAH</t>
+  </si>
+  <si>
+    <t>DEDE SAPUTRA</t>
+  </si>
+  <si>
+    <t>YAYAH NURHIDAYAH</t>
+  </si>
+  <si>
+    <t>NAURA MAULIDA SIDQIYYAH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD NIZAM</t>
+  </si>
+  <si>
+    <t>HASANAH</t>
+  </si>
+  <si>
+    <t>RUNISAH</t>
+  </si>
+  <si>
+    <t>JAJANG NURJAMAN</t>
+  </si>
+  <si>
+    <t>ILIH MUFLIHAH</t>
+  </si>
+  <si>
+    <t>FARHAN PRATAMA</t>
+  </si>
+  <si>
+    <t>SAEPULOH</t>
+  </si>
+  <si>
+    <t>ELI NURELIYAH</t>
+  </si>
+  <si>
+    <t>AMIRA NUR SYAHIRA</t>
+  </si>
+  <si>
+    <t>OTONG</t>
+  </si>
+  <si>
+    <t>NURHIDAYAH</t>
+  </si>
+  <si>
+    <t>SURYAMAN AL PURKON</t>
+  </si>
+  <si>
+    <t>MUHAMAD TOHA</t>
+  </si>
+  <si>
+    <t>DEWI HERNINGSIH</t>
+  </si>
+  <si>
+    <t>RIFKY MAHESA PUTRA</t>
+  </si>
+  <si>
+    <t>TARMAN</t>
+  </si>
+  <si>
+    <t>MARNI SUMARNI</t>
+  </si>
+  <si>
+    <t>SITI JAKIYATUL MUSTAFIDAH</t>
+  </si>
+  <si>
+    <t>EROM</t>
+  </si>
+  <si>
+    <t>CECE INDRA KURNIAWAN</t>
+  </si>
+  <si>
+    <t>AGUS GUNAWAN</t>
+  </si>
+  <si>
+    <t>NINING YUNINGSIH</t>
+  </si>
+  <si>
+    <t>ALFIAN SAPUTRA</t>
+  </si>
+  <si>
+    <t>FATHAN</t>
+  </si>
+  <si>
+    <t>RUDI GUNAWAN</t>
+  </si>
+  <si>
+    <t>ROSMIATI</t>
+  </si>
+  <si>
+    <t>MULYATI</t>
+  </si>
+  <si>
+    <t>TINA NUROSE KAMILA AGUSTINA</t>
+  </si>
+  <si>
+    <t>DEDE JAMALUDIN</t>
+  </si>
+  <si>
+    <t>NENENG HABIBAH</t>
   </si>
 </sst>
 </file>
@@ -450,7 +635,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -499,7 +684,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -824,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -865,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -876,11 +1061,11 @@
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>006</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>009</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>conf!$A$2</f>
@@ -895,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -906,11 +1091,11 @@
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>010</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>006</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>conf!$A$2</f>
@@ -925,22 +1110,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>005</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>012</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>conf!$A$2</f>
@@ -955,22 +1140,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>007</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G5" s="4" t="str">
         <f>conf!$A$2</f>
@@ -985,10 +1170,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -996,11 +1181,11 @@
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>009</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>002</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1015,22 +1200,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>003</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>009</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1045,14 +1230,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1060,7 +1245,7 @@
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>015</v>
       </c>
       <c r="G8" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1075,22 +1260,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>014</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1105,22 +1290,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>011</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="G10" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1135,10 +1320,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1150,7 +1335,7 @@
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>006</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1165,22 +1350,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>009</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>008</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1195,22 +1380,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>007</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>012</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1225,22 +1410,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>011</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>011</v>
       </c>
       <c r="G14" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1255,10 +1440,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1266,11 +1451,11 @@
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>003</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>015</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1285,10 +1470,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1296,11 +1481,11 @@
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>010</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>002</v>
       </c>
       <c r="G16" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1315,22 +1500,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>004</v>
       </c>
       <c r="F17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>014</v>
       </c>
       <c r="G17" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1345,22 +1530,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>004</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>011</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1375,14 +1560,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1390,7 +1575,7 @@
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="G19" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1405,22 +1590,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>011</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>008</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1435,22 +1620,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>005</v>
       </c>
       <c r="F21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>015</v>
       </c>
       <c r="G21" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1465,22 +1650,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>006</v>
       </c>
       <c r="F22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>008</v>
       </c>
       <c r="G22" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1495,22 +1680,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>012</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>014</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1525,22 +1710,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>012</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>012</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1555,22 +1740,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>001</v>
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>011</v>
       </c>
       <c r="G25" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1582,64 +1767,64 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="D26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>004</v>
       </c>
       <c r="F26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>015</v>
       </c>
       <c r="G26" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H26" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>003</v>
       </c>
       <c r="F27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="G27" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H27" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="D28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1658,204 +1843,204 @@
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G29" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H29" t="s">
         <v>55</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
-      </c>
-      <c r="F29" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
-      </c>
-      <c r="G29" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H29" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G30" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H30" t="s">
         <v>56</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
-      </c>
-      <c r="F30" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H30" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B31" s="1" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="D31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>002</v>
       </c>
       <c r="F31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>015</v>
       </c>
       <c r="G31" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H31" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="D32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>014</v>
       </c>
       <c r="F32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>015</v>
       </c>
       <c r="G32" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H32" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>013</v>
       </c>
       <c r="F33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>001</v>
       </c>
       <c r="G33" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H33" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="D34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>002</v>
       </c>
       <c r="F34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>011</v>
       </c>
       <c r="G34" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H34" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>004</v>
       </c>
       <c r="F35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>003</v>
       </c>
       <c r="G35" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H35" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1863,138 +2048,138 @@
       </c>
       <c r="E36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>008</v>
       </c>
       <c r="F36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>003</v>
       </c>
       <c r="G36" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>007</v>
       </c>
       <c r="F37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>014</v>
       </c>
       <c r="G37" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H37" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>007</v>
       </c>
       <c r="F38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>007</v>
       </c>
       <c r="G38" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H38" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>005</v>
       </c>
       <c r="F39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>007</v>
       </c>
       <c r="G39" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H39" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="F40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="G40" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H40" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -2002,22 +2187,22 @@
       </c>
       <c r="F41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>004</v>
       </c>
       <c r="G41" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H41" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2025,80 +2210,80 @@
       </c>
       <c r="E42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>004</v>
       </c>
       <c r="F42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="G42" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H42" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>003</v>
       </c>
       <c r="F43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>003</v>
       </c>
       <c r="G43" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H43" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>013</v>
       </c>
       <c r="F44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>006</v>
       </c>
       <c r="G44" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H44" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2106,107 +2291,107 @@
       </c>
       <c r="E45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>007</v>
       </c>
       <c r="F45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="G45" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H45" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="D46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>012</v>
       </c>
       <c r="F46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>015</v>
       </c>
       <c r="G46" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H46" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>005</v>
       </c>
       <c r="F47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>014</v>
       </c>
       <c r="G47" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H47" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>002</v>
       </c>
       <c r="F48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="G48" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H48" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B49" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2214,234 +2399,1746 @@
       </c>
       <c r="E49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>009</v>
       </c>
       <c r="F49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>001</v>
       </c>
       <c r="G49" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H49" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="D50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>005</v>
       </c>
       <c r="F50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="G50" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="D51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>015</v>
       </c>
       <c r="F51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>001</v>
       </c>
       <c r="G51" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H51" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>010</v>
       </c>
       <c r="F52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>015</v>
       </c>
       <c r="G52" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H52" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B53" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="D53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="F53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>013</v>
       </c>
       <c r="G53" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H53" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="D54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>007</v>
       </c>
       <c r="F54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="G54" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H54" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>010</v>
       </c>
       <c r="F55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>004</v>
       </c>
       <c r="G55" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H55" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="D56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>004</v>
       </c>
       <c r="F56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>008</v>
       </c>
       <c r="G56" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H56" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G57" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E58" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F58" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G58" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B59" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E59" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F59" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G59" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E60" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F60" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G60" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E61" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F61" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G61" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D62" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E62" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F62" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G62" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D63" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E63" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F63" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G63" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E64" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F64" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G64" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E65" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F65" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G65" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E66" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F66" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G66" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D67" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E67" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F67" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G67" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E68" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F68" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G68" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H68" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E69" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F69" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G69" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D70" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E70" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F70" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G70" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D71" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E71" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F71" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G71" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E72" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F72" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G72" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D73" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E73" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F73" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G73" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E74" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F74" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G74" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E75" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F75" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G75" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E76" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F76" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G76" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E77" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F77" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G77" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H77" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B78" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D78" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E78" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F78" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G78" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E79" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F79" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G79" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D80" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E80" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F80" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G80" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H80" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B81" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D81" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E81" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F81" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G81" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H81" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D82" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E82" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F82" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G82" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H82" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B83" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E83" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F83" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G83" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B84" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D84" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E84" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F84" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G84" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H84" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B85" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E85" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F85" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G85" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D86" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E86" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F86" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G86" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H86" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B87" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D87" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E87" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F87" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G87" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H87" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B88" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D88" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E88" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F88" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G88" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H88" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B89" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D89" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E89" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F89" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G89" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H89" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="2" t="str">
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D90" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E90" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F90" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G90" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H90" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D91" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
         <v>Pajagan</v>
       </c>
-      <c r="E57" s="2" t="str">
+      <c r="E91" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F91" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G91" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H91" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D92" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E92" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F92" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G92" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H92" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D93" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E93" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
         <v>013</v>
       </c>
-      <c r="F57" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+      <c r="F93" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G93" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H93" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D94" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E94" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F94" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G94" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H94" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B95" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D95" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E95" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F95" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G95" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H95" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D96" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E96" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F96" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G96" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H96" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D97" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E97" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
         <v>001</v>
       </c>
-      <c r="G57" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H57" t="s">
-        <v>138</v>
+      <c r="F97" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G97" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H97" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B98" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D98" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E98" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F98" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G98" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H98" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B99" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D99" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E99" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F99" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G99" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H99" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B100" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D100" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E100" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F100" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G100" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H100" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B101" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D101" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E101" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F101" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G101" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H101" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B102" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D102" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E102" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F102" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G102" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H102" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B103" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D103" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E103" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F103" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G103" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H103" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B104" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D104" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E104" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F104" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G104" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H104" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B105" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D105" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E105" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F105" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G105" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H105" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B106" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D106" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E106" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F106" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G106" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H106" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B107" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D107" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E107" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F107" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G107" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H107" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B108" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D108" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E108" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F108" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G108" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H108" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B109" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D109" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E109" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F109" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G109" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H109" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B110" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D110" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E110" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F110" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G110" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H110" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B111" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D111" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E111" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F111" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G111" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H111" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B112" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D112" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E112" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F112" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G112" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H112" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B113" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D113" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E113" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F113" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G113" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H113" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
